--- a/data/middle.xlsx
+++ b/data/middle.xlsx
@@ -19,7 +19,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="118">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
   <x:si>
     <x:t>070-7097-1901</x:t>
   </x:si>
@@ -345,7 +351,7 @@
     <x:t>배곧라라중학교</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+    <x:t xml:space="preserve"> 비고</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 주소</x:t>
@@ -354,10 +360,13 @@
     <x:t xml:space="preserve"> 학구</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
   </x:si>
   <x:si>
     <x:t>특수/순회학급 배치 학생 수</x:t>
@@ -366,13 +375,14 @@
     <x:t>일반학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
+    <x:r>
+      <x:t>37.4351</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>126.7834</x:t>
+    </x:r>
   </x:si>
 </x:sst>
 </file>
@@ -512,7 +522,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -583,6 +593,9 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -912,57 +925,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B1" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
+      <x:c r="H1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="I1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>111</x:v>
-      </x:c>
       <x:c r="K1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>0</x:v>
@@ -974,7 +987,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J2" s="6"/>
       <x:c r="K2" s="7">
@@ -986,34 +999,34 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="8" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G3" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H3" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K3" s="7">
         <x:v>37.351028001392201</x:v>
@@ -1024,19 +1037,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A4" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F4" s="10">
         <x:v>2</x:v>
@@ -1048,7 +1061,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J4" s="6"/>
       <x:c r="K4" s="7">
@@ -1060,19 +1073,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="76.84999999999999431566">
       <x:c r="A5" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="10">
         <x:v>1</x:v>
@@ -1084,7 +1097,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="7">
@@ -1096,19 +1109,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F6" s="10">
         <x:v>1</x:v>
@@ -1120,7 +1133,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="7">
@@ -1132,19 +1145,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F7" s="10">
         <x:v>2</x:v>
@@ -1156,7 +1169,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J7" s="6"/>
       <x:c r="K7" s="7">
@@ -1168,19 +1181,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="10">
         <x:v>2</x:v>
@@ -1192,7 +1205,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J8" s="6"/>
       <x:c r="K8" s="7">
@@ -1204,19 +1217,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="12">
         <x:v>3</x:v>
@@ -1228,7 +1241,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J9" s="6"/>
       <x:c r="K9" s="7">
@@ -1240,19 +1253,19 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F10" s="10">
         <x:v>2</x:v>
@@ -1264,7 +1277,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J10" s="6"/>
       <x:c r="K10" s="7">
@@ -1276,19 +1289,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A11" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>2</x:v>
@@ -1300,7 +1313,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J11" s="6"/>
       <x:c r="K11" s="7">
@@ -1312,19 +1325,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F12" s="10">
         <x:v>2</x:v>
@@ -1336,7 +1349,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J12" s="6"/>
       <x:c r="K12" s="7">
@@ -1348,19 +1361,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="12">
         <x:v>4</x:v>
@@ -1372,7 +1385,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="7">
@@ -1384,19 +1397,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A14" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="10">
         <x:v>2</x:v>
@@ -1408,7 +1421,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J14" s="6"/>
       <x:c r="K14" s="7">
@@ -1420,19 +1433,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F15" s="10">
         <x:v>2</x:v>
@@ -1444,7 +1457,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J15" s="6"/>
       <x:c r="K15" s="7">
@@ -1456,19 +1469,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="10">
         <x:v>2</x:v>
@@ -1480,7 +1493,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J16" s="6"/>
       <x:c r="K16" s="7">
@@ -1492,19 +1505,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F17" s="10">
         <x:v>1</x:v>
@@ -1516,7 +1529,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J17" s="6"/>
       <x:c r="K17" s="7">
@@ -1528,19 +1541,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F18" s="10">
         <x:v>1</x:v>
@@ -1552,7 +1565,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I18" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J18" s="6"/>
       <x:c r="K18" s="7">
@@ -1564,19 +1577,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F19" s="10">
         <x:v>3</x:v>
@@ -1588,7 +1601,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J19" s="6"/>
       <x:c r="K19" s="7">
@@ -1600,22 +1613,22 @@
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F20" s="10" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G20" s="4">
         <x:v>4</x:v>
@@ -1624,33 +1637,33 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J20" s="6" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="K20" s="7">
-        <x:v>37.516313374032599</x:v>
-      </x:c>
-      <x:c r="L20" s="7">
-        <x:v>127.078578189811</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="L20" s="14" t="s">
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A21" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F21" s="10">
         <x:v>2</x:v>
@@ -1662,7 +1675,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J21" s="6"/>
       <x:c r="K21" s="7">
@@ -1674,19 +1687,19 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F22" s="10">
         <x:v>2</x:v>
@@ -1698,7 +1711,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J22" s="6"/>
       <x:c r="K22" s="7">
@@ -1710,19 +1723,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F23" s="10">
         <x:v>1</x:v>
@@ -1734,7 +1747,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I23" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J23" s="6"/>
       <x:c r="K23" s="7">
@@ -1746,19 +1759,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F24" s="13">
         <x:v>1</x:v>
@@ -1770,7 +1783,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J24" s="6"/>
       <x:c r="K24" s="7">
@@ -1782,19 +1795,19 @@
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F25" s="10">
         <x:v>1</x:v>
@@ -1806,7 +1819,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I25" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J25" s="6"/>
       <x:c r="K25" s="7">
@@ -1818,19 +1831,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F26" s="10">
         <x:v>2</x:v>
@@ -1842,7 +1855,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J26" s="6"/>
       <x:c r="K26" s="7">
@@ -1854,19 +1867,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F27" s="10">
         <x:v>1</x:v>
@@ -1878,7 +1891,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J27" s="6"/>
       <x:c r="K27" s="7">
@@ -1890,19 +1903,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F28" s="2">
         <x:v>0</x:v>
@@ -1914,7 +1927,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J28" s="6"/>
       <x:c r="K28" s="7">
@@ -1926,19 +1939,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F29" s="10">
         <x:v>1</x:v>
@@ -1950,7 +1963,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J29" s="6"/>
       <x:c r="K29" s="7">
@@ -1961,7 +1974,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>

--- a/data/middle.xlsx
+++ b/data/middle.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
   <x:si>
     <x:t>보조인력 배치 유/무</x:t>
   </x:si>
@@ -377,6 +377,16 @@
   <x:si>
     <x:r>
       <x:t>37.4351</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>37.359424</x:t>
+    </x:r>
+  </x:si>
+  <x:si>
+    <x:r>
+      <x:t>126.731386</x:t>
     </x:r>
   </x:si>
   <x:si>
@@ -1604,11 +1614,11 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="J19" s="6"/>
-      <x:c r="K19" s="7">
-        <x:v>37.445994150157702</x:v>
-      </x:c>
-      <x:c r="L19" s="7">
-        <x:v>126.905439201376</x:v>
+      <x:c r="K19" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="L19" s="14" t="s">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
@@ -1646,7 +1656,7 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="L20" s="14" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12" ht="39.54999999999999715783">

--- a/data/middle.xlsx
+++ b/data/middle.xlsx
@@ -21,343 +21,361 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
   <x:si>
+    <x:t>070-7097-1901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-5272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-1800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-490-4800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡로 117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2491</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 1학급/시간제 3학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-7900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-505-1834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-2045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7158-9000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-487-7342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-506-1230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 금오로 640</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행로 60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-2616-9728</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-3032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0916</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-7304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거북섬남로 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-0073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-2800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-3424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(중)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 52번길 23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로54번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로111번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하상로 14-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현순환로 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대야동 377-70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 88-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자봉길 299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 374번길 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천서로 373번길 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2421번길 72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 298번길 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행로 144번길 36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>논곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복합/시간제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대흥중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라라중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.7834</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.359424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.731386</x:t>
+  </x:si>
+  <x:si>
     <x:t>보조인력 배치 유/무</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1901</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-5272</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-1800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-490-4800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡로 117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2491</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특 1학급/시간제 3학급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-7900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-505-1834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-2045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7158-9000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-487-7342</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-506-1230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0309</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 640</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행로 60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0414</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-2616-9728</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-3032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0916</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-7304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 거북섬남로 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1527</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-0073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화로 71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0471</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-2800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-3424</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(중)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 52번길 23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로54번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로111번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하상로 14-7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현순환로 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대야동 377-70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 88-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자봉길 299</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 205</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 374번길 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천서로 373번길 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2421번길 72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 298번길 28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행로 144번길 36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>논곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복합/시간제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대흥중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 학교설립별</x:t>
@@ -366,33 +384,7 @@
     <x:t xml:space="preserve"> 연락처</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>37.4351</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>37.359424</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>126.731386</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:t>126.7834</x:t>
-    </x:r>
+    <x:t>37.4351</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -935,22 +927,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>113</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="G1" t="s">
         <x:v>116</x:v>
@@ -959,33 +951,33 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>0</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>0</x:v>
@@ -997,7 +989,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J2" s="6"/>
       <x:c r="K2" s="7">
@@ -1009,34 +1001,34 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G3" s="9" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G3" s="9" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="H3" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K3" s="7">
         <x:v>37.351028001392201</x:v>
@@ -1047,19 +1039,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A4" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F4" s="10">
         <x:v>2</x:v>
@@ -1071,7 +1063,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J4" s="6"/>
       <x:c r="K4" s="7">
@@ -1083,19 +1075,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="76.84999999999999431566">
       <x:c r="A5" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="10">
         <x:v>1</x:v>
@@ -1107,7 +1099,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="7">
@@ -1119,19 +1111,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F6" s="10">
         <x:v>1</x:v>
@@ -1143,7 +1135,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="7">
@@ -1155,19 +1147,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A7" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F7" s="10">
         <x:v>2</x:v>
@@ -1179,7 +1171,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J7" s="6"/>
       <x:c r="K7" s="7">
@@ -1191,19 +1183,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A8" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="10">
         <x:v>2</x:v>
@@ -1215,7 +1207,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J8" s="6"/>
       <x:c r="K8" s="7">
@@ -1227,19 +1219,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="12">
         <x:v>3</x:v>
@@ -1251,7 +1243,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J9" s="6"/>
       <x:c r="K9" s="7">
@@ -1263,19 +1255,19 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="10">
         <x:v>2</x:v>
@@ -1287,7 +1279,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J10" s="6"/>
       <x:c r="K10" s="7">
@@ -1299,19 +1291,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A11" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>2</x:v>
@@ -1323,7 +1315,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J11" s="6"/>
       <x:c r="K11" s="7">
@@ -1335,19 +1327,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="10">
         <x:v>2</x:v>
@@ -1359,7 +1351,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J12" s="6"/>
       <x:c r="K12" s="7">
@@ -1371,19 +1363,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F13" s="12">
         <x:v>4</x:v>
@@ -1395,7 +1387,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="7">
@@ -1407,19 +1399,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A14" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F14" s="10">
         <x:v>2</x:v>
@@ -1431,7 +1423,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J14" s="6"/>
       <x:c r="K14" s="7">
@@ -1443,19 +1435,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="10">
         <x:v>2</x:v>
@@ -1467,7 +1459,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J15" s="6"/>
       <x:c r="K15" s="7">
@@ -1479,19 +1471,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F16" s="10">
         <x:v>2</x:v>
@@ -1503,7 +1495,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J16" s="6"/>
       <x:c r="K16" s="7">
@@ -1515,19 +1507,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F17" s="10">
         <x:v>1</x:v>
@@ -1539,7 +1531,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J17" s="6"/>
       <x:c r="K17" s="7">
@@ -1551,19 +1543,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F18" s="10">
         <x:v>1</x:v>
@@ -1575,7 +1567,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I18" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J18" s="6"/>
       <x:c r="K18" s="7">
@@ -1587,19 +1579,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="10">
         <x:v>3</x:v>
@@ -1611,34 +1603,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J19" s="6"/>
       <x:c r="K19" s="14" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="L19" s="14" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F20" s="10" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G20" s="4">
         <x:v>4</x:v>
@@ -1647,33 +1639,33 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J20" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K20" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="L20" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A21" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F21" s="10">
         <x:v>2</x:v>
@@ -1685,7 +1677,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J21" s="6"/>
       <x:c r="K21" s="7">
@@ -1697,19 +1689,19 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F22" s="10">
         <x:v>2</x:v>
@@ -1721,7 +1713,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J22" s="6"/>
       <x:c r="K22" s="7">
@@ -1733,19 +1725,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F23" s="10">
         <x:v>1</x:v>
@@ -1757,7 +1749,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I23" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J23" s="6"/>
       <x:c r="K23" s="7">
@@ -1769,19 +1761,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F24" s="13">
         <x:v>1</x:v>
@@ -1793,7 +1785,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J24" s="6"/>
       <x:c r="K24" s="7">
@@ -1805,19 +1797,19 @@
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F25" s="10">
         <x:v>1</x:v>
@@ -1829,7 +1821,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I25" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J25" s="6"/>
       <x:c r="K25" s="7">
@@ -1841,19 +1833,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A26" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F26" s="10">
         <x:v>2</x:v>
@@ -1865,7 +1857,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J26" s="6"/>
       <x:c r="K26" s="7">
@@ -1877,19 +1869,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F27" s="10">
         <x:v>1</x:v>
@@ -1901,7 +1893,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J27" s="6"/>
       <x:c r="K27" s="7">
@@ -1913,19 +1905,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F28" s="2">
         <x:v>0</x:v>
@@ -1937,7 +1929,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J28" s="6"/>
       <x:c r="K28" s="7">
@@ -1949,19 +1941,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F29" s="10">
         <x:v>1</x:v>
@@ -1973,7 +1965,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J29" s="6"/>
       <x:c r="K29" s="7">
@@ -1984,7 +1976,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>

--- a/data/middle.xlsx
+++ b/data/middle.xlsx
@@ -19,23 +19,227 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
+  <x:si>
+    <x:t>경도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행로 144번길 36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천서로 373번길 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 374번길 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 298번길 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2421번길 72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대흥중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복합/시간제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>논곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라라중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학교설립별</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 연락처</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산현중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(중)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보조인력 배치 유/무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.359424</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.731386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 1학급/시간제 3학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-5272</x:t>
+  </x:si>
   <x:si>
     <x:t>070-7097-1901</x:t>
   </x:si>
   <x:si>
-    <x:t>031-8042-5272</x:t>
-  </x:si>
-  <x:si>
     <x:t>031-8063-1800</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 배곧4로 72</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 역전로 435</x:t>
-  </x:si>
-  <x:si>
     <x:t>031-490-4800</x:t>
   </x:si>
   <x:si>
@@ -45,346 +249,136 @@
     <x:t>031-8042-2491</x:t>
   </x:si>
   <x:si>
-    <x:t>복특 1학급/시간제 3학급</x:t>
-  </x:si>
-  <x:si>
     <x:t>031-503-7900</x:t>
   </x:si>
   <x:si>
+    <x:t>경기도 시흥시 은행로 60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-487-7342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-2616-9728</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-3032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0916</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-7304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-2045</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-505-1834</x:t>
   </x:si>
   <x:si>
-    <x:t>031-503-2045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3500</x:t>
+    <x:t>031-365-8200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-506-1230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0309</x:t>
   </x:si>
   <x:si>
     <x:t>070-7158-9000</x:t>
   </x:si>
   <x:si>
-    <x:t>031-365-8200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-487-7342</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-506-1230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0309</x:t>
-  </x:si>
-  <x:si>
     <x:t>경기도 시흥시 금오로 640</x:t>
   </x:si>
   <x:si>
     <x:t>070-7097-0700</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 은행로 60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0414</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-2616-9728</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-3032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0916</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-7304</x:t>
+    <x:t>070-7097-0471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-2800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-3424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-0073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로54번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 52번길 23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로111번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하상로 14-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 66</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 거북섬남로 70</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 목감남서로 66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1527</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-0073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화로 71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0471</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-2800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-3424</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(중)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 52번길 23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로54번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로111번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하상로 14-7</x:t>
+    <x:t>경기도 시흥시 목감둘레로 205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자봉길 299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 88-1</x:t>
   </x:si>
   <x:si>
     <x:t>경기도 시흥시 장현순환로 100</x:t>
   </x:si>
   <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 63</x:t>
+  </x:si>
+  <x:si>
     <x:t>경기도 시흥시 대야동 377-70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 88-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자봉길 299</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 205</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 374번길 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천서로 373번길 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2421번길 72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 298번길 28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행로 144번길 36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>논곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복합/시간제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대흥중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>126.7834</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37.359424</x:t>
-  </x:si>
-  <x:si>
-    <x:t>126.731386</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37.4351</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -927,57 +921,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
-        <x:v>118</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>119</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>110</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>109</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>120</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>112</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>116</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>117</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>115</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>108</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>68</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>67</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>0</x:v>
@@ -989,7 +983,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J2" s="6"/>
       <x:c r="K2" s="7">
@@ -1001,34 +995,34 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F3" s="8" t="s">
-        <x:v>86</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G3" s="9" t="s">
-        <x:v>66</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H3" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K3" s="7">
         <x:v>37.351028001392201</x:v>
@@ -1039,19 +1033,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A4" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F4" s="10">
         <x:v>2</x:v>
@@ -1063,7 +1057,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J4" s="6"/>
       <x:c r="K4" s="7">
@@ -1075,19 +1069,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="76.84999999999999431566">
       <x:c r="A5" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F5" s="10">
         <x:v>1</x:v>
@@ -1099,7 +1093,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="7">
@@ -1111,19 +1105,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F6" s="10">
         <x:v>1</x:v>
@@ -1135,7 +1129,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="7">
@@ -1147,19 +1141,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F7" s="10">
         <x:v>2</x:v>
@@ -1171,7 +1165,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J7" s="6"/>
       <x:c r="K7" s="7">
@@ -1183,19 +1177,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F8" s="10">
         <x:v>2</x:v>
@@ -1207,7 +1201,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J8" s="6"/>
       <x:c r="K8" s="7">
@@ -1219,19 +1213,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="12">
         <x:v>3</x:v>
@@ -1243,7 +1237,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J9" s="6"/>
       <x:c r="K9" s="7">
@@ -1255,19 +1249,19 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="10">
         <x:v>2</x:v>
@@ -1279,7 +1273,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J10" s="6"/>
       <x:c r="K10" s="7">
@@ -1291,19 +1285,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A11" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>2</x:v>
@@ -1315,7 +1309,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J11" s="6"/>
       <x:c r="K11" s="7">
@@ -1327,19 +1321,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A12" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F12" s="10">
         <x:v>2</x:v>
@@ -1351,7 +1345,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J12" s="6"/>
       <x:c r="K12" s="7">
@@ -1363,19 +1357,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F13" s="12">
         <x:v>4</x:v>
@@ -1387,7 +1381,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="7">
@@ -1399,19 +1393,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A14" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F14" s="10">
         <x:v>2</x:v>
@@ -1423,7 +1417,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J14" s="6"/>
       <x:c r="K14" s="7">
@@ -1435,19 +1429,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F15" s="10">
         <x:v>2</x:v>
@@ -1459,7 +1453,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J15" s="6"/>
       <x:c r="K15" s="7">
@@ -1471,19 +1465,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F16" s="10">
         <x:v>2</x:v>
@@ -1495,7 +1489,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J16" s="6"/>
       <x:c r="K16" s="7">
@@ -1507,19 +1501,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F17" s="10">
         <x:v>1</x:v>
@@ -1531,7 +1525,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J17" s="6"/>
       <x:c r="K17" s="7">
@@ -1543,19 +1537,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F18" s="10">
         <x:v>1</x:v>
@@ -1567,7 +1561,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I18" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J18" s="6"/>
       <x:c r="K18" s="7">
@@ -1579,19 +1573,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F19" s="10">
         <x:v>3</x:v>
@@ -1603,34 +1597,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J19" s="6"/>
       <x:c r="K19" s="14" t="s">
-        <x:v>113</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L19" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F20" s="10" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G20" s="4">
         <x:v>4</x:v>
@@ -1639,33 +1633,33 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J20" s="6" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="K20" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="L20" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K20" s="14">
+        <x:v>37.4342443821362</x:v>
+      </x:c>
+      <x:c r="L20" s="14">
+        <x:v>126.782361232894</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A21" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F21" s="10">
         <x:v>2</x:v>
@@ -1677,7 +1671,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J21" s="6"/>
       <x:c r="K21" s="7">
@@ -1689,19 +1683,19 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A22" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F22" s="10">
         <x:v>2</x:v>
@@ -1713,7 +1707,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J22" s="6"/>
       <x:c r="K22" s="7">
@@ -1725,19 +1719,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F23" s="10">
         <x:v>1</x:v>
@@ -1749,7 +1743,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I23" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J23" s="6"/>
       <x:c r="K23" s="7">
@@ -1761,19 +1755,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F24" s="13">
         <x:v>1</x:v>
@@ -1785,7 +1779,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J24" s="6"/>
       <x:c r="K24" s="7">
@@ -1797,19 +1791,19 @@
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F25" s="10">
         <x:v>1</x:v>
@@ -1821,7 +1815,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I25" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J25" s="6"/>
       <x:c r="K25" s="7">
@@ -1833,19 +1827,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F26" s="10">
         <x:v>2</x:v>
@@ -1857,7 +1851,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J26" s="6"/>
       <x:c r="K26" s="7">
@@ -1869,19 +1863,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F27" s="10">
         <x:v>1</x:v>
@@ -1893,7 +1887,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J27" s="6"/>
       <x:c r="K27" s="7">
@@ -1905,19 +1899,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F28" s="2">
         <x:v>0</x:v>
@@ -1929,7 +1923,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J28" s="6"/>
       <x:c r="K28" s="7">
@@ -1941,19 +1935,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F29" s="10">
         <x:v>1</x:v>
@@ -1965,7 +1959,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J29" s="6"/>
       <x:c r="K29" s="7">

--- a/data/middle.xlsx
+++ b/data/middle.xlsx
@@ -19,7 +19,331 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="120">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
+  <x:si>
+    <x:t>031-503-2045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 금오로 640</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-2800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-487-7342</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 매화로 71</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0063</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-3424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 능곡로 117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-503-7900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-365-8200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-2616-9728</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복특 1학급/시간제 3학급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-7304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-5272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-1901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7158-9000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8099-9920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 역전로 435</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0916</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-317-3032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8042-2491</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-505-1834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행로 60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-506-1230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-433-0073</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-8063-1800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화나래중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 배곧4로 72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-364-3500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-490-4800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>031-363-1527</x:t>
+  </x:si>
+  <x:si>
+    <x:t>070-7097-0414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧해솔중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/ 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧라라중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>서해중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>응곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은계중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥은행중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥매화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시화중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조남중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥가온중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군자중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>목감중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정왕중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>논곡중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소래중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대흥중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>송운중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복합/시간제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연성중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.4351</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배곧중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>함현중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4/ 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시흥능곡중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월곶중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(특수/순회/일반)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신천중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>군서미래국제학교(중)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.7834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.359424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>126.731386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 하상로 14-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군자봉길 299</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장곡로54번길 14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 거북섬남로 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 포도원로 88-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대야동 377-70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 큰솔로 52번길 23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감남서로 66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 월곶해안로 63</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 목감둘레로 205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 대은로111번길 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 군서마을로 102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 장현순환로 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 433-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천서로 373번길 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 정왕대로 298번길 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 은행로 144번길 36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 수인로2421번길 72</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 서울대학로 150-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경기도 시흥시 옥구천동로 374번길 39</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공립</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사립</x:t>
+  </x:si>
   <x:si>
     <x:t>경도</x:t>
   </x:si>
@@ -27,358 +351,40 @@
     <x:t>위도</x:t>
   </x:si>
   <x:si>
-    <x:t>경기도 시흥시 은행로 144번길 36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천서로 373번길 18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 374번길 39</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 정왕대로 298번길 28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 옥구천동로 433-11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 150-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 수인로2421번길 72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>함현중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧해솔중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은계중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>서해중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군자중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대흥중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>송운중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>조남중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정왕중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>목감중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24/ 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4/ 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연성중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복합/시간제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>논곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥매화중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소래중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥은행중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월곶중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>응곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배곧라라중학교</x:t>
+    <x:t>산현중학교(복합특수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한국글로벌중학교</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 학교명</x:t>
   </x:si>
   <x:si>
-    <x:t>시화중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥가온중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시흥능곡중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장곡중학교</x:t>
+    <x:t xml:space="preserve"> 연락처</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 학교설립별</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 연락처</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사립</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산현중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군서미래국제학교(중)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한국글로벌중학교</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(특수/순회/일반)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신천중학교(복합특수)</x:t>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
   </x:si>
   <x:si>
     <x:t>보조인력 배치 유/무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37.359424</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 특수/순회학급수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>126.731386</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 역전로 435</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복특 1학급/시간제 3학급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-5272</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-1901</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8063-1800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 배곧4로 72</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-490-4800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 능곡로 117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2491</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-7900</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 은행로 60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0414</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-487-7342</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8042-2790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-364-3500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-2616-9728</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-3032</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0916</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-317-7304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-503-2045</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-505-1834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-8200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-506-1230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0309</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7158-9000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 금오로 640</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0700</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0471</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-2800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-365-3424</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>070-7097-0063</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 매화로 71</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시화나래중학교(복합특수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-8099-9920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-363-1527</x:t>
-  </x:si>
-  <x:si>
-    <x:t>031-433-0073</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장곡로54번길 14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 큰솔로 52번길 23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대은로111번길 10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군서마을로 102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 하상로 14-7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감남서로 66</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 거북섬남로 70</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 목감둘레로 205</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 군자봉길 299</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 포도원로 88-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 장현순환로 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 서울대학로 255</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 월곶해안로 63</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경기도 시흥시 대야동 377-70</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -921,57 +927,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
-        <x:v>43</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>48</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>52</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>51</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E1" t="s">
-        <x:v>49</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>65</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>98</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>99</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I1" t="s">
-        <x:v>63</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>50</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>1</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>0</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>0</x:v>
@@ -983,7 +989,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J2" s="6"/>
       <x:c r="K2" s="7">
@@ -995,34 +1001,34 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F3" s="8" t="s">
-        <x:v>30</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G3" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H3" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K3" s="7">
         <x:v>37.351028001392201</x:v>
@@ -1033,19 +1039,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="10">
         <x:v>2</x:v>
@@ -1057,7 +1063,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J4" s="6"/>
       <x:c r="K4" s="7">
@@ -1069,19 +1075,19 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="76.84999999999999431566">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>119</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="10">
         <x:v>1</x:v>
@@ -1093,7 +1099,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="7">
@@ -1105,19 +1111,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="10">
         <x:v>1</x:v>
@@ -1129,7 +1135,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="7">
@@ -1141,19 +1147,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A7" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F7" s="10">
         <x:v>2</x:v>
@@ -1165,7 +1171,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J7" s="6"/>
       <x:c r="K7" s="7">
@@ -1177,19 +1183,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="10">
         <x:v>2</x:v>
@@ -1201,7 +1207,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J8" s="6"/>
       <x:c r="K8" s="7">
@@ -1213,19 +1219,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F9" s="12">
         <x:v>3</x:v>
@@ -1237,7 +1243,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J9" s="6"/>
       <x:c r="K9" s="7">
@@ -1249,19 +1255,19 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="10">
         <x:v>2</x:v>
@@ -1273,7 +1279,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J10" s="6"/>
       <x:c r="K10" s="7">
@@ -1285,19 +1291,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>2</x:v>
@@ -1309,7 +1315,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J11" s="6"/>
       <x:c r="K11" s="7">
@@ -1321,19 +1327,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F12" s="10">
         <x:v>2</x:v>
@@ -1345,7 +1351,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J12" s="6"/>
       <x:c r="K12" s="7">
@@ -1357,19 +1363,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A13" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F13" s="12">
         <x:v>4</x:v>
@@ -1381,7 +1387,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="7">
@@ -1393,19 +1399,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="10">
         <x:v>2</x:v>
@@ -1417,7 +1423,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J14" s="6"/>
       <x:c r="K14" s="7">
@@ -1429,19 +1435,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F15" s="10">
         <x:v>2</x:v>
@@ -1453,7 +1459,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J15" s="6"/>
       <x:c r="K15" s="7">
@@ -1465,19 +1471,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F16" s="10">
         <x:v>2</x:v>
@@ -1489,7 +1495,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J16" s="6"/>
       <x:c r="K16" s="7">
@@ -1501,19 +1507,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F17" s="10">
         <x:v>1</x:v>
@@ -1522,10 +1528,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H17" s="4">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I17" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J17" s="6"/>
       <x:c r="K17" s="7">
@@ -1537,19 +1543,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F18" s="10">
         <x:v>1</x:v>
@@ -1561,7 +1567,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I18" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J18" s="6"/>
       <x:c r="K18" s="7">
@@ -1573,19 +1579,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F19" s="10">
         <x:v>3</x:v>
@@ -1597,34 +1603,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J19" s="6"/>
       <x:c r="K19" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="L19" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F20" s="10" t="s">
-        <x:v>68</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G20" s="4">
         <x:v>4</x:v>
@@ -1633,33 +1639,33 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J20" s="6" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K20" s="14">
-        <x:v>37.4342443821362</x:v>
-      </x:c>
-      <x:c r="L20" s="14">
-        <x:v>126.782361232894</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K20" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L20" s="14" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F21" s="10">
         <x:v>2</x:v>
@@ -1671,7 +1677,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J21" s="6"/>
       <x:c r="K21" s="7">
@@ -1683,19 +1689,19 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F22" s="10">
         <x:v>2</x:v>
@@ -1707,7 +1713,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J22" s="6"/>
       <x:c r="K22" s="7">
@@ -1719,19 +1725,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F23" s="10">
         <x:v>1</x:v>
@@ -1740,10 +1746,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H23" s="4">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J23" s="6"/>
       <x:c r="K23" s="7">
@@ -1755,19 +1761,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="13">
         <x:v>1</x:v>
@@ -1779,7 +1785,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J24" s="6"/>
       <x:c r="K24" s="7">
@@ -1791,19 +1797,19 @@
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F25" s="10">
         <x:v>1</x:v>
@@ -1815,7 +1821,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I25" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J25" s="6"/>
       <x:c r="K25" s="7">
@@ -1827,19 +1833,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F26" s="10">
         <x:v>2</x:v>
@@ -1851,7 +1857,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J26" s="6"/>
       <x:c r="K26" s="7">
@@ -1863,19 +1869,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F27" s="10">
         <x:v>1</x:v>
@@ -1887,7 +1893,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J27" s="6"/>
       <x:c r="K27" s="7">
@@ -1899,19 +1905,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F28" s="2">
         <x:v>0</x:v>
@@ -1923,7 +1929,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J28" s="6"/>
       <x:c r="K28" s="7">
@@ -1935,19 +1941,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F29" s="10">
         <x:v>1</x:v>
@@ -1959,7 +1965,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="J29" s="6"/>
       <x:c r="K29" s="7">

--- a/data/middle.xlsx
+++ b/data/middle.xlsx
@@ -21,6 +21,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="122">
   <x:si>
+    <x:t>일반학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수/순회학급 배치 학생 수</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 주소</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 학구</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> 비고</x:t>
+  </x:si>
+  <x:si>
     <x:t>031-503-2045</x:t>
   </x:si>
   <x:si>
@@ -360,13 +375,7 @@
     <x:t xml:space="preserve"> 특수/순회학급수</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 주소</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 학구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> 비고</x:t>
+    <x:t>보조인력 배치 유/무</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 학교명</x:t>
@@ -376,15 +385,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 학교설립별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수/순회학급 배치 학생 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보조인력 배치 유/무</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -927,57 +927,57 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I1" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="C1" t="s">
+      <x:c r="J1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D1" t="s">
+      <x:c r="L1" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="K1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="L1" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A2" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F2" s="2">
         <x:v>0</x:v>
@@ -989,7 +989,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J2" s="6"/>
       <x:c r="K2" s="7">
@@ -1001,34 +1001,34 @@
     </x:row>
     <x:row r="3" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A3" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="8" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G3" s="9" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H3" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K3" s="7">
         <x:v>37.351028001392201</x:v>
@@ -1039,19 +1039,19 @@
     </x:row>
     <x:row r="4" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A4" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="10">
         <x:v>2</x:v>
@@ -1063,31 +1063,31 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J4" s="6"/>
       <x:c r="K4" s="7">
-        <x:v>37.414628988045898</x:v>
+        <x:v>37.389011600000003</x:v>
       </x:c>
       <x:c r="L4" s="7">
-        <x:v>126.71217984892201</x:v>
+        <x:v>126.85752599999999</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12" ht="76.84999999999999431566">
       <x:c r="A5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="10">
         <x:v>1</x:v>
@@ -1099,7 +1099,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I5" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="7">
@@ -1111,19 +1111,19 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A6" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="10">
         <x:v>1</x:v>
@@ -1135,7 +1135,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="7">
@@ -1147,19 +1147,19 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="10">
         <x:v>2</x:v>
@@ -1171,7 +1171,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J7" s="6"/>
       <x:c r="K7" s="7">
@@ -1183,19 +1183,19 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F8" s="10">
         <x:v>2</x:v>
@@ -1207,7 +1207,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J8" s="6"/>
       <x:c r="K8" s="7">
@@ -1219,19 +1219,19 @@
     </x:row>
     <x:row r="9" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A9" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F9" s="12">
         <x:v>3</x:v>
@@ -1243,7 +1243,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J9" s="6"/>
       <x:c r="K9" s="7">
@@ -1255,19 +1255,19 @@
     </x:row>
     <x:row r="10" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="10">
         <x:v>2</x:v>
@@ -1279,7 +1279,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J10" s="6"/>
       <x:c r="K10" s="7">
@@ -1291,19 +1291,19 @@
     </x:row>
     <x:row r="11" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F11" s="10">
         <x:v>2</x:v>
@@ -1315,7 +1315,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J11" s="6"/>
       <x:c r="K11" s="7">
@@ -1327,19 +1327,19 @@
     </x:row>
     <x:row r="12" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A12" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F12" s="10">
         <x:v>2</x:v>
@@ -1351,7 +1351,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J12" s="6"/>
       <x:c r="K12" s="7">
@@ -1363,19 +1363,19 @@
     </x:row>
     <x:row r="13" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="12">
         <x:v>4</x:v>
@@ -1387,7 +1387,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="7">
@@ -1399,19 +1399,19 @@
     </x:row>
     <x:row r="14" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F14" s="10">
         <x:v>2</x:v>
@@ -1423,7 +1423,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J14" s="6"/>
       <x:c r="K14" s="7">
@@ -1435,19 +1435,19 @@
     </x:row>
     <x:row r="15" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F15" s="10">
         <x:v>2</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J15" s="6"/>
       <x:c r="K15" s="7">
@@ -1471,19 +1471,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F16" s="10">
         <x:v>2</x:v>
@@ -1495,7 +1495,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J16" s="6"/>
       <x:c r="K16" s="7">
@@ -1507,19 +1507,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F17" s="10">
         <x:v>1</x:v>
@@ -1531,7 +1531,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I17" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J17" s="6"/>
       <x:c r="K17" s="7">
@@ -1543,19 +1543,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F18" s="10">
         <x:v>1</x:v>
@@ -1567,7 +1567,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I18" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J18" s="6"/>
       <x:c r="K18" s="7">
@@ -1579,19 +1579,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F19" s="10">
         <x:v>3</x:v>
@@ -1603,34 +1603,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J19" s="6"/>
       <x:c r="K19" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L19" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="10" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G20" s="4">
         <x:v>4</x:v>
@@ -1639,33 +1639,33 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J20" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K20" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="L20" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F21" s="10">
         <x:v>2</x:v>
@@ -1677,7 +1677,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J21" s="6"/>
       <x:c r="K21" s="7">
@@ -1689,19 +1689,19 @@
     </x:row>
     <x:row r="22" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F22" s="10">
         <x:v>2</x:v>
@@ -1713,7 +1713,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J22" s="6"/>
       <x:c r="K22" s="7">
@@ -1725,19 +1725,19 @@
     </x:row>
     <x:row r="23" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F23" s="10">
         <x:v>1</x:v>
@@ -1749,7 +1749,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J23" s="6"/>
       <x:c r="K23" s="7">
@@ -1761,19 +1761,19 @@
     </x:row>
     <x:row r="24" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F24" s="13">
         <x:v>1</x:v>
@@ -1785,7 +1785,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J24" s="6"/>
       <x:c r="K24" s="7">
@@ -1797,19 +1797,19 @@
     </x:row>
     <x:row r="25" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F25" s="10">
         <x:v>1</x:v>
@@ -1821,7 +1821,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I25" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J25" s="6"/>
       <x:c r="K25" s="7">
@@ -1833,19 +1833,19 @@
     </x:row>
     <x:row r="26" spans="1:12" ht="52.70000000000000284217">
       <x:c r="A26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F26" s="10">
         <x:v>2</x:v>
@@ -1857,7 +1857,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I26" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J26" s="6"/>
       <x:c r="K26" s="7">
@@ -1869,19 +1869,19 @@
     </x:row>
     <x:row r="27" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F27" s="10">
         <x:v>1</x:v>
@@ -1893,7 +1893,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J27" s="6"/>
       <x:c r="K27" s="7">
@@ -1905,19 +1905,19 @@
     </x:row>
     <x:row r="28" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A28" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F28" s="2">
         <x:v>0</x:v>
@@ -1929,7 +1929,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J28" s="6"/>
       <x:c r="K28" s="7">
@@ -1941,19 +1941,19 @@
     </x:row>
     <x:row r="29" spans="1:12" ht="39.54999999999999715783">
       <x:c r="A29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F29" s="10">
         <x:v>1</x:v>
@@ -1965,7 +1965,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J29" s="6"/>
       <x:c r="K29" s="7">
